--- a/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
+++ b/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94775796-E163-4B7A-B0A3-600323C7DE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073FE79A-9C15-4BC5-A7EA-2D3280D3F597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitShoulder" sheetId="1" r:id="rId1"/>
@@ -847,7 +847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -856,8 +856,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -872,6 +879,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -905,17 +917,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -932,9 +947,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -972,9 +987,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1007,9 +1022,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1042,9 +1074,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1219,60 +1268,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1436,7 +1485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1647,7 @@
       </c>
       <c r="BB2" s="2"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>258</v>
       </c>
@@ -1761,7 +1810,7 @@
       </c>
       <c r="BB3" s="2"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
@@ -1924,7 +1973,7 @@
       </c>
       <c r="BB4" s="2"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2087,7 +2136,7 @@
       </c>
       <c r="BB5" s="2"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2250,7 +2299,7 @@
       </c>
       <c r="BB6" s="2"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
@@ -2413,7 +2462,7 @@
       </c>
       <c r="BB7" s="2"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>65</v>
       </c>
@@ -2576,7 +2625,7 @@
       </c>
       <c r="BB8" s="2"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>67</v>
       </c>
@@ -2739,7 +2788,7 @@
       </c>
       <c r="BB9" s="2"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2902,7 +2951,7 @@
       </c>
       <c r="BB10" s="2"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>71</v>
       </c>
@@ -3065,7 +3114,7 @@
       </c>
       <c r="BB11" s="2"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>73</v>
       </c>
@@ -3228,7 +3277,7 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
@@ -3391,7 +3440,7 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>77</v>
       </c>
@@ -3554,7 +3603,7 @@
       </c>
       <c r="BB14" s="2"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
@@ -3717,7 +3766,7 @@
       </c>
       <c r="BB15" s="2"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>81</v>
       </c>
@@ -3751,8 +3800,8 @@
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>49</v>
+      <c r="L16" s="5">
+        <v>51</v>
       </c>
       <c r="M16" s="3">
         <v>-1</v>
@@ -3880,7 +3929,7 @@
       </c>
       <c r="BB16" s="2"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>83</v>
       </c>
@@ -4043,7 +4092,7 @@
       </c>
       <c r="BB17" s="2"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>85</v>
       </c>
@@ -4206,7 +4255,7 @@
       </c>
       <c r="BB18" s="2"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>87</v>
       </c>
@@ -4369,7 +4418,7 @@
       </c>
       <c r="BB19" s="2"/>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>88</v>
       </c>
@@ -4532,7 +4581,7 @@
       </c>
       <c r="BB20" s="2"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>90</v>
       </c>
@@ -4695,7 +4744,7 @@
       </c>
       <c r="BB21" s="2"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>92</v>
       </c>
@@ -4858,7 +4907,7 @@
       </c>
       <c r="BB22" s="2"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>94</v>
       </c>
@@ -5021,7 +5070,7 @@
       </c>
       <c r="BB23" s="2"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>262</v>
       </c>
@@ -5184,7 +5233,7 @@
       </c>
       <c r="BB24" s="2"/>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>98</v>
       </c>
@@ -5347,7 +5396,7 @@
       </c>
       <c r="BB25" s="2"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>100</v>
       </c>
@@ -5510,7 +5559,7 @@
       </c>
       <c r="BB26" s="2"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>101</v>
       </c>
@@ -5673,7 +5722,7 @@
       </c>
       <c r="BB27" s="2"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>102</v>
       </c>
@@ -5836,7 +5885,7 @@
       </c>
       <c r="BB28" s="2"/>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>104</v>
       </c>
@@ -5999,7 +6048,7 @@
       </c>
       <c r="BB29" s="2"/>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>106</v>
       </c>
@@ -6162,7 +6211,7 @@
       </c>
       <c r="BB30" s="2"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>108</v>
       </c>
@@ -6325,7 +6374,7 @@
       </c>
       <c r="BB31" s="2"/>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>110</v>
       </c>
@@ -6488,7 +6537,7 @@
       </c>
       <c r="BB32" s="2"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>112</v>
       </c>
@@ -6651,7 +6700,7 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>114</v>
       </c>
@@ -6814,7 +6863,7 @@
       </c>
       <c r="BB34" s="2"/>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>116</v>
       </c>
@@ -6977,7 +7026,7 @@
       </c>
       <c r="BB35" s="2"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>118</v>
       </c>
@@ -7140,7 +7189,7 @@
       </c>
       <c r="BB36" s="2"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>120</v>
       </c>
@@ -7174,8 +7223,8 @@
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="3">
-        <v>49</v>
+      <c r="L37" s="5">
+        <v>51</v>
       </c>
       <c r="M37" s="3">
         <v>-1</v>
@@ -7303,7 +7352,7 @@
       </c>
       <c r="BB37" s="2"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>122</v>
       </c>
@@ -7466,7 +7515,7 @@
       </c>
       <c r="BB38" s="2"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>124</v>
       </c>
@@ -7629,7 +7678,7 @@
       </c>
       <c r="BB39" s="2"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>126</v>
       </c>
@@ -7792,7 +7841,7 @@
       </c>
       <c r="BB40" s="2"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>127</v>
       </c>
@@ -7955,7 +8004,7 @@
       </c>
       <c r="BB41" s="2"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>129</v>
       </c>
@@ -8118,7 +8167,7 @@
       </c>
       <c r="BB42" s="2"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>131</v>
       </c>
@@ -8281,7 +8330,7 @@
       </c>
       <c r="BB43" s="2"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>133</v>
       </c>
@@ -8444,7 +8493,7 @@
       </c>
       <c r="BB44" s="2"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>265</v>
       </c>
@@ -8607,7 +8656,7 @@
       </c>
       <c r="BB45" s="2"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>137</v>
       </c>
@@ -8770,7 +8819,7 @@
       </c>
       <c r="BB46" s="2"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>139</v>
       </c>
@@ -8933,7 +8982,7 @@
       </c>
       <c r="BB47" s="2"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>141</v>
       </c>
@@ -9096,7 +9145,7 @@
       </c>
       <c r="BB48" s="2"/>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>143</v>
       </c>
@@ -9259,7 +9308,7 @@
       </c>
       <c r="BB49" s="2"/>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>145</v>
       </c>
@@ -9422,7 +9471,7 @@
       </c>
       <c r="BB50" s="2"/>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>147</v>
       </c>
@@ -9585,7 +9634,7 @@
       </c>
       <c r="BB51" s="2"/>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>149</v>
       </c>
@@ -9748,7 +9797,7 @@
       </c>
       <c r="BB52" s="2"/>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>151</v>
       </c>
@@ -9911,7 +9960,7 @@
       </c>
       <c r="BB53" s="2"/>
     </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>153</v>
       </c>
@@ -10074,7 +10123,7 @@
       </c>
       <c r="BB54" s="2"/>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>155</v>
       </c>
@@ -10237,7 +10286,7 @@
       </c>
       <c r="BB55" s="2"/>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>157</v>
       </c>
@@ -10400,7 +10449,7 @@
       </c>
       <c r="BB56" s="2"/>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>159</v>
       </c>
@@ -10563,7 +10612,7 @@
       </c>
       <c r="BB57" s="2"/>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>161</v>
       </c>
@@ -10726,7 +10775,7 @@
       </c>
       <c r="BB58" s="2"/>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>163</v>
       </c>
@@ -10889,7 +10938,7 @@
       </c>
       <c r="BB59" s="2"/>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>165</v>
       </c>
@@ -11052,7 +11101,7 @@
       </c>
       <c r="BB60" s="2"/>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>167</v>
       </c>
@@ -11215,7 +11264,7 @@
       </c>
       <c r="BB61" s="2"/>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>169</v>
       </c>
@@ -11378,7 +11427,7 @@
       </c>
       <c r="BB62" s="2"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>171</v>
       </c>
@@ -11541,7 +11590,7 @@
       </c>
       <c r="BB63" s="2"/>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>173</v>
       </c>
@@ -11704,7 +11753,7 @@
       </c>
       <c r="BB64" s="2"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>175</v>
       </c>
@@ -11867,7 +11916,7 @@
       </c>
       <c r="BB65" s="2"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>177</v>
       </c>
@@ -12030,7 +12079,7 @@
       </c>
       <c r="BB66" s="2"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>180</v>
       </c>
@@ -12193,7 +12242,7 @@
       </c>
       <c r="BB67" s="2"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>182</v>
       </c>
@@ -12356,7 +12405,7 @@
       </c>
       <c r="BB68" s="2"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>184</v>
       </c>
@@ -12519,7 +12568,7 @@
       </c>
       <c r="BB69" s="2"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>186</v>
       </c>
@@ -12682,7 +12731,7 @@
       </c>
       <c r="BB70" s="2"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>188</v>
       </c>
@@ -12845,7 +12894,7 @@
       </c>
       <c r="BB71" s="2"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>190</v>
       </c>
@@ -13008,7 +13057,7 @@
       </c>
       <c r="BB72" s="2"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>192</v>
       </c>
@@ -13171,7 +13220,7 @@
       </c>
       <c r="BB73" s="2"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>194</v>
       </c>
@@ -13334,7 +13383,7 @@
       </c>
       <c r="BB74" s="2"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>196</v>
       </c>
@@ -13497,7 +13546,7 @@
       </c>
       <c r="BB75" s="2"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>198</v>
       </c>
@@ -13660,7 +13709,7 @@
       </c>
       <c r="BB76" s="2"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>200</v>
       </c>
@@ -13823,7 +13872,7 @@
       </c>
       <c r="BB77" s="2"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>202</v>
       </c>
@@ -13986,7 +14035,7 @@
       </c>
       <c r="BB78" s="2"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>204</v>
       </c>
@@ -14149,7 +14198,7 @@
       </c>
       <c r="BB79" s="2"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>206</v>
       </c>
@@ -14312,7 +14361,7 @@
       </c>
       <c r="BB80" s="2"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>208</v>
       </c>
@@ -14475,7 +14524,7 @@
       </c>
       <c r="BB81" s="2"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>210</v>
       </c>
@@ -14638,7 +14687,7 @@
       </c>
       <c r="BB82" s="2"/>
     </row>
-    <row r="83" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>212</v>
       </c>
@@ -14801,7 +14850,7 @@
       </c>
       <c r="BB83" s="2"/>
     </row>
-    <row r="84" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>214</v>
       </c>
@@ -14964,7 +15013,7 @@
       </c>
       <c r="BB84" s="2"/>
     </row>
-    <row r="85" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>216</v>
       </c>
@@ -15127,7 +15176,7 @@
       </c>
       <c r="BB85" s="2"/>
     </row>
-    <row r="86" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>218</v>
       </c>
@@ -15299,60 +15348,60 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BH86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="12" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>220</v>
       </c>
@@ -15534,7 +15583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>UnitShoulder!A2</f>
         <v>Code</v>
@@ -15746,7 +15795,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>UnitShoulder!A3</f>
         <v>uns0006</v>
@@ -15958,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>UnitShoulder!A4</f>
         <v>unsh001</v>
@@ -16170,7 +16219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>UnitShoulder!A5</f>
         <v>unsh002</v>
@@ -16382,7 +16431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>UnitShoulder!A6</f>
         <v>unsh003</v>
@@ -16594,7 +16643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>UnitShoulder!A7</f>
         <v>unsh004</v>
@@ -16806,7 +16855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>UnitShoulder!A8</f>
         <v>unsh005</v>
@@ -17018,7 +17067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>UnitShoulder!A9</f>
         <v>unsh006</v>
@@ -17230,7 +17279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>UnitShoulder!A10</f>
         <v>unsh007</v>
@@ -17442,7 +17491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>UnitShoulder!A11</f>
         <v>unsh008</v>
@@ -17654,7 +17703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>UnitShoulder!A12</f>
         <v>unsh009</v>
@@ -17866,7 +17915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>UnitShoulder!A13</f>
         <v>unsh010</v>
@@ -18078,7 +18127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>UnitShoulder!A14</f>
         <v>unsh011</v>
@@ -18290,7 +18339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>UnitShoulder!A15</f>
         <v>unsh012</v>
@@ -18502,7 +18551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UnitShoulder!A16</f>
         <v>unsh013</v>
@@ -18642,7 +18691,7 @@
       </c>
       <c r="AO16">
         <f>UnitShoulder!L16</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP16">
         <f>UnitShoulder!N16</f>
@@ -18714,7 +18763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UnitShoulder!A17</f>
         <v>unsh014</v>
@@ -18926,7 +18975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UnitShoulder!A18</f>
         <v>unsh015</v>
@@ -19138,7 +19187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UnitShoulder!A19</f>
         <v>unsh016</v>
@@ -19350,7 +19399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UnitShoulder!A20</f>
         <v>unsh017</v>
@@ -19562,7 +19611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UnitShoulder!A21</f>
         <v>unsh018</v>
@@ -19774,7 +19823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UnitShoulder!A22</f>
         <v>unsh019</v>
@@ -19986,7 +20035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UnitShoulder!A23</f>
         <v>unsh020</v>
@@ -20198,7 +20247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UnitShoulder!A24</f>
         <v>uns0002</v>
@@ -20410,7 +20459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UnitShoulder!A25</f>
         <v>unsh021</v>
@@ -20622,7 +20671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UnitShoulder!A26</f>
         <v>unsh022</v>
@@ -20834,7 +20883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UnitShoulder!A27</f>
         <v>unsh023</v>
@@ -21046,7 +21095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UnitShoulder!A28</f>
         <v>unsh024</v>
@@ -21258,7 +21307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UnitShoulder!A29</f>
         <v>unsh025</v>
@@ -21470,7 +21519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UnitShoulder!A30</f>
         <v>unsh026</v>
@@ -21682,7 +21731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UnitShoulder!A31</f>
         <v>unsh027</v>
@@ -21894,7 +21943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UnitShoulder!A32</f>
         <v>unsh028</v>
@@ -22106,7 +22155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UnitShoulder!A33</f>
         <v>unsh029</v>
@@ -22318,7 +22367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UnitShoulder!A34</f>
         <v>unsh030</v>
@@ -22530,7 +22579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UnitShoulder!A35</f>
         <v>unsh031</v>
@@ -22742,7 +22791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UnitShoulder!A36</f>
         <v>unsh032</v>
@@ -22954,7 +23003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UnitShoulder!A37</f>
         <v>unsh033</v>
@@ -23094,7 +23143,7 @@
       </c>
       <c r="AO37">
         <f>UnitShoulder!L37</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP37">
         <f>UnitShoulder!N37</f>
@@ -23166,7 +23215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UnitShoulder!A38</f>
         <v>unsh034</v>
@@ -23378,7 +23427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UnitShoulder!A39</f>
         <v>unsh035</v>
@@ -23590,7 +23639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UnitShoulder!A40</f>
         <v>unsh036</v>
@@ -23802,7 +23851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UnitShoulder!A41</f>
         <v>unsh037</v>
@@ -24014,7 +24063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UnitShoulder!A42</f>
         <v>unsh038</v>
@@ -24226,7 +24275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UnitShoulder!A43</f>
         <v>unsh039</v>
@@ -24438,7 +24487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UnitShoulder!A44</f>
         <v>unsh040</v>
@@ -24650,7 +24699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UnitShoulder!A45</f>
         <v>uns0004</v>
@@ -24862,7 +24911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UnitShoulder!A46</f>
         <v>unsh041</v>
@@ -25074,7 +25123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>UnitShoulder!A47</f>
         <v>unsh042</v>
@@ -25286,7 +25335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>UnitShoulder!A48</f>
         <v>unsh043</v>
@@ -25498,7 +25547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>UnitShoulder!A49</f>
         <v>unsh044</v>
@@ -25710,7 +25759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>UnitShoulder!A50</f>
         <v>unsh045</v>
@@ -25922,7 +25971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>UnitShoulder!A51</f>
         <v>unsh046</v>
@@ -26134,7 +26183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>UnitShoulder!A52</f>
         <v>unsh047</v>
@@ -26346,7 +26395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>UnitShoulder!A53</f>
         <v>unsh048</v>
@@ -26558,7 +26607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>UnitShoulder!A54</f>
         <v>unsh049</v>
@@ -26770,7 +26819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>UnitShoulder!A55</f>
         <v>unsh050</v>
@@ -26982,7 +27031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>UnitShoulder!A56</f>
         <v>unsh051</v>
@@ -27194,7 +27243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>UnitShoulder!A57</f>
         <v>unsh052</v>
@@ -27406,7 +27455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>UnitShoulder!A58</f>
         <v>unsh053</v>
@@ -27618,7 +27667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>UnitShoulder!A59</f>
         <v>unsh054</v>
@@ -27830,7 +27879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>UnitShoulder!A60</f>
         <v>unsh055</v>
@@ -28042,7 +28091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>UnitShoulder!A61</f>
         <v>unsh056</v>
@@ -28254,7 +28303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>UnitShoulder!A62</f>
         <v>unsh057</v>
@@ -28466,7 +28515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>UnitShoulder!A63</f>
         <v>unsh058</v>
@@ -28678,7 +28727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>UnitShoulder!A64</f>
         <v>unsh059</v>
@@ -28890,7 +28939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>UnitShoulder!A65</f>
         <v>unsh060</v>
@@ -29102,7 +29151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>UnitShoulder!A66</f>
         <v>unsn000</v>
@@ -29314,7 +29363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>UnitShoulder!A67</f>
         <v>unsh061</v>
@@ -29526,7 +29575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>UnitShoulder!A68</f>
         <v>unsh062</v>
@@ -29738,7 +29787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>UnitShoulder!A69</f>
         <v>unsh063</v>
@@ -29950,7 +29999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>UnitShoulder!A70</f>
         <v>unsh064</v>
@@ -30162,7 +30211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>UnitShoulder!A71</f>
         <v>unsh065</v>
@@ -30374,7 +30423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>UnitShoulder!A72</f>
         <v>unsh066</v>
@@ -30586,7 +30635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>UnitShoulder!A73</f>
         <v>unsh067</v>
@@ -30798,7 +30847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>UnitShoulder!A74</f>
         <v>unsh068</v>
@@ -31010,7 +31059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>UnitShoulder!A75</f>
         <v>unsh069</v>
@@ -31222,7 +31271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>UnitShoulder!A76</f>
         <v>unsh070</v>
@@ -31434,7 +31483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>UnitShoulder!A77</f>
         <v>unsh071</v>
@@ -31646,7 +31695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>UnitShoulder!A78</f>
         <v>unsh072</v>
@@ -31858,7 +31907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>UnitShoulder!A79</f>
         <v>unsh073</v>
@@ -32070,7 +32119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>UnitShoulder!A80</f>
         <v>unsh074</v>
@@ -32282,7 +32331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>UnitShoulder!A81</f>
         <v>unsh075</v>
@@ -32494,7 +32543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>UnitShoulder!A82</f>
         <v>unsh076</v>
@@ -32706,7 +32755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f>UnitShoulder!A83</f>
         <v>unsh077</v>
@@ -32918,7 +32967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f>UnitShoulder!A84</f>
         <v>unsh078</v>
@@ -33130,7 +33179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f>UnitShoulder!A85</f>
         <v>unsh079</v>
@@ -33342,7 +33391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f>UnitShoulder!A86</f>
         <v>unsh080</v>
@@ -33563,9 +33612,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -33576,7 +33625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>225</v>
       </c>
@@ -33585,7 +33634,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
@@ -33594,7 +33643,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -33603,7 +33652,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -33612,7 +33661,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -33621,7 +33670,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -33630,7 +33679,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -33639,7 +33688,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -33648,7 +33697,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -33657,7 +33706,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -33666,7 +33715,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -33675,7 +33724,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -33684,7 +33733,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -33693,7 +33742,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -33702,7 +33751,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -33711,7 +33760,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -33720,7 +33769,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -33729,7 +33778,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -33738,7 +33787,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -33747,7 +33796,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -33756,7 +33805,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -33765,7 +33814,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -33774,7 +33823,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -33783,7 +33832,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -33792,7 +33841,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -33801,7 +33850,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -33810,7 +33859,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -33819,7 +33868,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -33828,7 +33877,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -33837,7 +33886,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -33846,7 +33895,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -33855,7 +33904,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -33864,7 +33913,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -33873,7 +33922,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -33882,7 +33931,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -33891,7 +33940,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -33900,7 +33949,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -33909,7 +33958,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -33918,7 +33967,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -33927,7 +33976,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -33936,7 +33985,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -33945,7 +33994,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -33954,7 +34003,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -33963,7 +34012,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -33972,7 +34021,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -33981,7 +34030,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -33990,7 +34039,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -33999,7 +34048,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -34008,7 +34057,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -34017,7 +34066,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -34026,7 +34075,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -34035,7 +34084,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -34044,7 +34093,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -34053,7 +34102,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -34062,7 +34111,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -34071,7 +34120,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -34080,7 +34129,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -34089,7 +34138,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -34098,7 +34147,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -34107,7 +34156,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -34116,7 +34165,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -34125,7 +34174,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -34134,7 +34183,7 @@
       </c>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -34143,7 +34192,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -34152,7 +34201,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -34161,7 +34210,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -34170,7 +34219,7 @@
       </c>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>65</v>
       </c>
@@ -34179,7 +34228,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>66</v>
       </c>
@@ -34188,7 +34237,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>67</v>
       </c>
@@ -34197,7 +34246,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>68</v>
       </c>
@@ -34206,7 +34255,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>69</v>
       </c>
@@ -34215,7 +34264,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>70</v>
       </c>
@@ -34224,7 +34273,7 @@
       </c>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>71</v>
       </c>
@@ -34233,7 +34282,7 @@
       </c>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>72</v>
       </c>
@@ -34242,7 +34291,7 @@
       </c>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>73</v>
       </c>
@@ -34251,7 +34300,7 @@
       </c>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>74</v>
       </c>
@@ -34260,7 +34309,7 @@
       </c>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>75</v>
       </c>
@@ -34269,7 +34318,7 @@
       </c>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>76</v>
       </c>
@@ -34278,7 +34327,7 @@
       </c>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>77</v>
       </c>
@@ -34287,7 +34336,7 @@
       </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>78</v>
       </c>
@@ -34296,7 +34345,7 @@
       </c>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>79</v>
       </c>
@@ -34305,7 +34354,7 @@
       </c>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>80</v>
       </c>
@@ -34314,7 +34363,7 @@
       </c>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>81</v>
       </c>
@@ -34323,7 +34372,7 @@
       </c>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>82</v>
       </c>
@@ -34332,7 +34381,7 @@
       </c>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>83</v>
       </c>

--- a/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
+++ b/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073FE79A-9C15-4BC5-A7EA-2D3280D3F597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE4B954-A456-497C-A51A-AEFA06A4F0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -847,7 +847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,8 +863,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,6 +891,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -917,20 +929,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6700,168 +6717,168 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:54" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>7</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="6">
         <v>4</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="6">
         <v>6</v>
       </c>
-      <c r="H34" s="3">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="H34" s="6">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6">
+        <v>2</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
         <v>45</v>
       </c>
-      <c r="M34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N34" s="3">
-        <v>2</v>
-      </c>
-      <c r="O34" s="3">
+      <c r="M34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="6">
+        <v>2</v>
+      </c>
+      <c r="O34" s="6">
         <v>78</v>
       </c>
-      <c r="P34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="2">
-        <v>1</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-      <c r="T34" s="3">
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="7">
+        <v>1</v>
+      </c>
+      <c r="S34" s="7">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6">
         <v>225</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="6">
         <v>3000</v>
       </c>
-      <c r="V34" s="2">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3">
-        <v>0</v>
-      </c>
-      <c r="X34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
+      <c r="V34" s="7">
+        <v>0</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0</v>
+      </c>
+      <c r="X34" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="6">
         <v>99</v>
       </c>
-      <c r="Z34" s="2">
+      <c r="Z34" s="7">
         <v>50</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AA34" s="7">
         <v>50</v>
       </c>
-      <c r="AB34" s="3">
+      <c r="AB34" s="5">
         <v>255</v>
       </c>
-      <c r="AC34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
+      <c r="AC34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
         <v>700000</v>
       </c>
-      <c r="AK34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="2">
+      <c r="AK34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="7">
         <v>14000</v>
       </c>
-      <c r="AN34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="2" t="str">
+      <c r="AN34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AQ34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>tunsh030</v>
       </c>
-      <c r="AZ34" s="3">
+      <c r="AZ34" s="6">
         <v>12</v>
       </c>
-      <c r="BA34" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB34" s="2"/>
+      <c r="BA34" s="6">
+        <v>2</v>
+      </c>
+      <c r="BB34" s="7"/>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">

--- a/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
+++ b/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE4B954-A456-497C-A51A-AEFA06A4F0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD01AEA-40AF-48EC-AF3C-FABEBFEF7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -934,7 +934,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -944,6 +944,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -6823,8 +6824,8 @@
       <c r="AI34" s="6">
         <v>0</v>
       </c>
-      <c r="AJ34" s="6">
-        <v>700000</v>
+      <c r="AJ34" s="9">
+        <v>90909382</v>
       </c>
       <c r="AK34" s="6">
         <v>0</v>
@@ -22416,7 +22417,7 @@
       </c>
       <c r="I34">
         <f>UnitShoulder!AJ34</f>
-        <v>700000</v>
+        <v>90909382</v>
       </c>
       <c r="J34">
         <f>UnitShoulder!AK34</f>

--- a/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
+++ b/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD01AEA-40AF-48EC-AF3C-FABEBFEF7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D19EAC-EFFB-452E-ACA1-D2B720A82EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitShoulder" sheetId="1" r:id="rId1"/>
@@ -871,7 +871,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,6 +896,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -934,7 +940,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -945,6 +951,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -965,9 +974,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1005,9 +1014,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1040,26 +1049,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1092,26 +1084,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3295,168 +3270,168 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="10">
         <v>3</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="10">
         <v>4</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="10">
         <v>5</v>
       </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>2</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
         <v>45</v>
       </c>
-      <c r="M13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N13" s="3">
-        <v>2</v>
-      </c>
-      <c r="O13" s="3">
+      <c r="M13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>2</v>
+      </c>
+      <c r="O13" s="10">
         <v>78</v>
       </c>
-      <c r="P13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R13" s="2">
-        <v>1</v>
-      </c>
-      <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
+      <c r="P13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="10">
         <v>225</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="10">
         <v>3000</v>
       </c>
-      <c r="V13" s="2">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
+      <c r="V13" s="11">
+        <v>0</v>
+      </c>
+      <c r="W13" s="10">
+        <v>0</v>
+      </c>
+      <c r="X13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="10">
         <v>99</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="Z13" s="11">
         <v>50</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AA13" s="11">
         <v>50</v>
       </c>
-      <c r="AB13" s="3">
-        <v>375</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="3">
-        <v>700000</v>
-      </c>
-      <c r="AK13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM13" s="2">
-        <v>14000</v>
-      </c>
-      <c r="AN13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY13" s="2" t="str">
+      <c r="AB13" s="10">
+        <v>275</v>
+      </c>
+      <c r="AC13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="AE13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>1500000</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="9">
+        <v>150000</v>
+      </c>
+      <c r="AN13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>tunsh010</v>
       </c>
-      <c r="AZ13" s="3">
+      <c r="AZ13" s="10">
         <v>12</v>
       </c>
-      <c r="BA13" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB13" s="2"/>
+      <c r="BA13" s="10">
+        <v>2</v>
+      </c>
+      <c r="BB13" s="11"/>
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -6825,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="9">
-        <v>90909382</v>
+        <v>1500000</v>
       </c>
       <c r="AK34" s="6">
         <v>0</v>
@@ -6833,8 +6808,8 @@
       <c r="AL34" s="6">
         <v>1</v>
       </c>
-      <c r="AM34" s="7">
-        <v>14000</v>
+      <c r="AM34" s="9">
+        <v>150000</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -17965,7 +17940,7 @@
       </c>
       <c r="I13">
         <f>UnitShoulder!AJ13</f>
-        <v>700000</v>
+        <v>1500000</v>
       </c>
       <c r="J13">
         <f>UnitShoulder!AK13</f>
@@ -18027,7 +18002,7 @@
       </c>
       <c r="AB13">
         <f>UnitShoulder!AB13</f>
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="AC13">
         <f>UnitShoulder!AE13</f>
@@ -22417,7 +22392,7 @@
       </c>
       <c r="I34">
         <f>UnitShoulder!AJ34</f>
-        <v>90909382</v>
+        <v>1500000</v>
       </c>
       <c r="J34">
         <f>UnitShoulder!AK34</f>

--- a/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
+++ b/gu_in/Item.edf/41_UnitShoulder/UnitShoulder.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D19EAC-EFFB-452E-ACA1-D2B720A82EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDE8E10-6A2F-4C52-A07F-8F517FEF2EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitShoulder" sheetId="1" r:id="rId1"/>
@@ -974,9 +974,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1014,9 +1014,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1049,9 +1049,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1084,9 +1101,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6800,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="9">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="AK34" s="6">
         <v>0</v>
@@ -6809,7 +6843,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="9">
-        <v>150000</v>
+        <v>909091</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -22392,7 +22426,7 @@
       </c>
       <c r="I34">
         <f>UnitShoulder!AJ34</f>
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="J34">
         <f>UnitShoulder!AK34</f>
